--- a/data/Ajan_traits_file.xlsx
+++ b/data/Ajan_traits_file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhruvakathuria/Documents/GitHub/Hierarchical_foliar_trait_estimation/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkathuri/Documents/GitHub/Hierarchical_foliar_trait_estimation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C4C70A-9DCB-384B-9D48-8E79CB4DFA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DED981-9685-674A-A830-1A16FBC0A48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1 - Traits" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="136">
   <si>
     <t>Traits</t>
   </si>
@@ -33,12 +33,6 @@
     <t>Sample id</t>
   </si>
   <si>
-    <t>Paper Link</t>
-  </si>
-  <si>
-    <t>Instrument name</t>
-  </si>
-  <si>
     <t>Chlorophyll abbreviation</t>
   </si>
   <si>
@@ -394,13 +388,95 @@
   </si>
   <si>
     <t>Measurement quantity</t>
+  </si>
+  <si>
+    <t>Linked Resources</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/jxb/err294 https://figshare.com/articles/Spectroscopic_determination_of_leaf_nutritional_morphological_and_metabolic_traits/745311</t>
+  </si>
+  <si>
+    <t>Instrument Manufacturer</t>
+  </si>
+  <si>
+    <t>Instrument model</t>
+  </si>
+  <si>
+    <t>analytical spectral devices</t>
+  </si>
+  <si>
+    <t>asd fieldspec 3</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>reflectance</t>
+  </si>
+  <si>
+    <t>https://www.nsf.gov/funding/pgm_summ.jsp?pims_id=503446 https://www.nsf.gov/awardsearch/showAward?AWD_ID=1342778&amp;HistoricalAwards=false</t>
+  </si>
+  <si>
+    <t>Chl g m2</t>
+  </si>
+  <si>
+    <t>g m2</t>
+  </si>
+  <si>
+    <t>guid</t>
+  </si>
+  <si>
+    <r>
+      <t>asd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF313534"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>asd inc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fieldspec3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF313534"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>asd fieldspec 3</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -458,6 +534,37 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF313534"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -479,7 +586,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -817,41 +924,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -908,28 +989,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -998,30 +1057,43 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1033,7 +1105,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1063,9 +1135,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1121,9 +1190,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1136,49 +1202,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2339,366 +2435,431 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.1640625" style="1" customWidth="1"/>
-    <col min="2" max="13" width="16.33203125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="16.33203125" style="1"/>
+    <col min="1" max="1" width="81" style="1" customWidth="1"/>
+    <col min="2" max="14" width="16.33203125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="I2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="49" t="s">
+      <c r="J2" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="139" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="50" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="38"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="44"/>
-    </row>
-    <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="4"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D3" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="49"/>
+    </row>
+    <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="54"/>
+    </row>
+    <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
+    </row>
+    <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="50"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="54"/>
+    </row>
+    <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="3"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L7" s="3"/>
+      <c r="M7" s="5"/>
+    </row>
+    <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="3"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L8" s="3"/>
+      <c r="M8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="3"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L9" s="3"/>
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="3"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L10" s="3"/>
+      <c r="M10" s="5"/>
+    </row>
+    <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="3"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L11" s="3"/>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="3"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L12" s="3"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="3"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L13" s="3"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="3"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L14" s="3"/>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="3"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="10"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L15" s="3"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="3"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="10"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L16" s="3"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="3"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="10"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L17" s="3"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="3"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L18" s="3"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="3"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L19" s="3"/>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="3"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="10"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L20" s="3"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="3"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L21" s="3"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="3"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:12" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="1:13" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="8"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="11"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
-      <c r="L23" s="9"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" display="https://doi.org/10.1093/jxb/err294" xr:uid="{6DDB035B-D28E-AE4A-A90A-621360FA05D0}"/>
+    <hyperlink ref="D3" r:id="rId2" tooltip="Filter by Instrument Manufacturer = analytical spectral devices" display="https://ecosis.org/search/%5B%7B%22Instrument Manufacturer%22%3A%22analytical spectral devices%22%7D%5D/0/6" xr:uid="{0078268D-0796-D640-8548-088803D4A3A9}"/>
+    <hyperlink ref="E3" r:id="rId3" tooltip="Filter by Instrument Model = asd fieldspec 3" display="https://ecosis.org/search/%5B%7B%22Instrument Model%22%3A%22asd fieldspec 3%22%7D%5D/0/6" xr:uid="{9C06EB64-CBCA-2043-B6C1-767456EAE503}"/>
+    <hyperlink ref="C4" r:id="rId4" display="https://www.nsf.gov/funding/pgm_summ.jsp?pims_id=503446" xr:uid="{93F35597-79AF-5A4D-A496-5DCF40363F86}"/>
+    <hyperlink ref="F4" r:id="rId5" tooltip="Filter by Target Type = leaf" display="https://ecosis.org/search/%5B%7B%22Target Type%22%3A%22leaf%22%7D%5D/0/6" xr:uid="{7EBB99B1-A6A1-034D-B6EC-94CB22436EAC}"/>
+    <hyperlink ref="G4" r:id="rId6" tooltip="Filter by Measurement Quantity = reflectance" display="https://ecosis.org/search/%5B%7B%22Measurement Quantity%22%3A%22reflectance%22%7D%5D/0/6" xr:uid="{4A82C68D-878D-974E-8026-FC64C53FE6DF}"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
   <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
@@ -2712,129 +2873,129 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="39.83203125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="44.83203125" style="13" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="1" width="34.83203125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="39.83203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="43" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="20" x14ac:dyDescent="0.15">
+      <c r="A2" s="15"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="16"/>
+    </row>
+    <row r="3" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B4" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="20" x14ac:dyDescent="0.15">
-      <c r="A2" s="16"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="17"/>
-    </row>
-    <row r="3" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A4" s="18" t="s">
+      <c r="C5" s="19"/>
+    </row>
+    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A5" s="18" t="s">
+      <c r="C6" s="19"/>
+    </row>
+    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A6" s="18" t="s">
+      <c r="C7" s="19"/>
+    </row>
+    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="19"/>
+    </row>
+    <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="19"/>
+    </row>
+    <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="19"/>
+    </row>
+    <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A7" s="18" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="19"/>
+    </row>
+    <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="20"/>
-    </row>
-    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="20"/>
-    </row>
-    <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="20"/>
-    </row>
-    <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A10" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="20"/>
-    </row>
-    <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A11" s="18" t="s">
+      <c r="B12" s="25"/>
+      <c r="C12" s="19"/>
+    </row>
+    <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.15">
+      <c r="A13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="20"/>
-    </row>
-    <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A12" s="18" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="19"/>
+    </row>
+    <row r="14" spans="1:3" ht="22" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="20"/>
-    </row>
-    <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.15">
-      <c r="A13" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="20"/>
-    </row>
-    <row r="14" spans="1:3" ht="22" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="22"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2846,683 +3007,683 @@
   <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="28"/>
+    <col min="1" max="16384" width="10.83203125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="29">
+      <c r="A1" s="28">
         <v>1</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="28">
+        <v>2</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="28">
+        <v>3</v>
+      </c>
+      <c r="B3" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="29">
-        <v>2</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="Q3" s="27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="28">
+        <v>4</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="29">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="Q4" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="T4" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="28">
+        <v>5</v>
+      </c>
+      <c r="B5" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="29">
-        <v>4</v>
-      </c>
-      <c r="B4" s="29" t="s">
+    </row>
+    <row r="6" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="28">
+        <v>6</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="Q4" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="T4" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U4" s="30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="29">
-        <v>5</v>
-      </c>
-      <c r="B5" s="29" t="s">
+    </row>
+    <row r="7" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="28">
+        <v>7</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="29">
-        <v>6</v>
-      </c>
-      <c r="B6" s="29" t="s">
+    <row r="8" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="28">
+        <v>8</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="29">
-        <v>7</v>
-      </c>
-      <c r="B7" s="29" t="s">
+    <row r="9" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A9" s="28">
+        <v>9</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="29">
-        <v>8</v>
-      </c>
-      <c r="B8" s="29" t="s">
+    <row r="10" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="28">
+        <v>10</v>
+      </c>
+      <c r="B10" s="28" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A9" s="29">
-        <v>9</v>
-      </c>
-      <c r="B9" s="29" t="s">
+    <row r="11" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A11" s="28">
+        <v>11</v>
+      </c>
+      <c r="B11" s="28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="29">
-        <v>10</v>
-      </c>
-      <c r="B10" s="29" t="s">
+    <row r="12" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A12" s="28">
+        <v>12</v>
+      </c>
+      <c r="B12" s="28" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="29">
-        <v>11</v>
-      </c>
-      <c r="B11" s="29" t="s">
+    <row r="13" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A13" s="28">
+        <v>13</v>
+      </c>
+      <c r="B13" s="28" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="29">
-        <v>12</v>
-      </c>
-      <c r="B12" s="29" t="s">
+    <row r="14" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A14" s="28">
+        <v>14</v>
+      </c>
+      <c r="B14" s="28" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13" s="29">
-        <v>13</v>
-      </c>
-      <c r="B13" s="29" t="s">
+    <row r="15" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A15" s="28">
+        <v>15</v>
+      </c>
+      <c r="B15" s="28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="29">
-        <v>14</v>
-      </c>
-      <c r="B14" s="29" t="s">
+    <row r="16" spans="1:21" ht="20" x14ac:dyDescent="0.2">
+      <c r="A16" s="28">
+        <v>16</v>
+      </c>
+      <c r="B16" s="28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="29">
-        <v>15</v>
-      </c>
-      <c r="B15" s="29" t="s">
+    <row r="17" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A17" s="28">
+        <v>17</v>
+      </c>
+      <c r="B17" s="28" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="29">
-        <v>16</v>
-      </c>
-      <c r="B16" s="29" t="s">
+    <row r="18" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A18" s="28">
+        <v>18</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A17" s="29">
-        <v>17</v>
-      </c>
-      <c r="B17" s="29" t="s">
+    <row r="19" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A19" s="28">
+        <v>19</v>
+      </c>
+      <c r="B19" s="28" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="29">
-        <v>18</v>
-      </c>
-      <c r="B18" s="29" t="s">
+    <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A20" s="28">
+        <v>20</v>
+      </c>
+      <c r="B20" s="28" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="29">
-        <v>19</v>
-      </c>
-      <c r="B19" s="29" t="s">
+    <row r="21" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A21" s="28">
+        <v>21</v>
+      </c>
+      <c r="B21" s="28" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="29">
-        <v>20</v>
-      </c>
-      <c r="B20" s="29" t="s">
+    <row r="22" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A22" s="28">
+        <v>22</v>
+      </c>
+      <c r="B22" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="29">
-        <v>21</v>
-      </c>
-      <c r="B21" s="29" t="s">
+    <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A23" s="28">
+        <v>23</v>
+      </c>
+      <c r="B23" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="29">
-        <v>22</v>
-      </c>
-      <c r="B22" s="29" t="s">
+    <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A24" s="28">
+        <v>24</v>
+      </c>
+      <c r="B24" s="28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="29">
-        <v>23</v>
-      </c>
-      <c r="B23" s="29" t="s">
+    <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A25" s="28">
+        <v>25</v>
+      </c>
+      <c r="B25" s="28" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="29">
-        <v>24</v>
-      </c>
-      <c r="B24" s="29" t="s">
+    <row r="26" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A26" s="28">
+        <v>26</v>
+      </c>
+      <c r="B26" s="28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25" s="29">
-        <v>25</v>
-      </c>
-      <c r="B25" s="29" t="s">
+    <row r="27" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A27" s="28">
+        <v>27</v>
+      </c>
+      <c r="B27" s="28" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="29">
-        <v>26</v>
-      </c>
-      <c r="B26" s="29" t="s">
+    <row r="28" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A28" s="28">
+        <v>28</v>
+      </c>
+      <c r="B28" s="28" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="29">
-        <v>27</v>
-      </c>
-      <c r="B27" s="29" t="s">
+    <row r="29" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A29" s="28">
+        <v>29</v>
+      </c>
+      <c r="B29" s="28" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="29">
-        <v>28</v>
-      </c>
-      <c r="B28" s="29" t="s">
+    <row r="30" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A30" s="28">
+        <v>30</v>
+      </c>
+      <c r="B30" s="28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A29" s="29">
-        <v>29</v>
-      </c>
-      <c r="B29" s="29" t="s">
+    <row r="31" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A31" s="28">
+        <v>31</v>
+      </c>
+      <c r="B31" s="28" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="29">
-        <v>30</v>
-      </c>
-      <c r="B30" s="29" t="s">
+    <row r="32" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A32" s="28">
+        <v>32</v>
+      </c>
+      <c r="B32" s="28" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="29">
-        <v>31</v>
-      </c>
-      <c r="B31" s="29" t="s">
+    <row r="33" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A33" s="28">
+        <v>33</v>
+      </c>
+      <c r="B33" s="28" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="29">
-        <v>32</v>
-      </c>
-      <c r="B32" s="29" t="s">
+    <row r="34" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A34" s="28">
+        <v>34</v>
+      </c>
+      <c r="B34" s="28" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="29">
-        <v>33</v>
-      </c>
-      <c r="B33" s="29" t="s">
+    <row r="35" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A35" s="28">
+        <v>35</v>
+      </c>
+      <c r="B35" s="28" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="29">
-        <v>34</v>
-      </c>
-      <c r="B34" s="29" t="s">
+    <row r="36" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A36" s="28">
+        <v>36</v>
+      </c>
+      <c r="B36" s="28" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="29">
-        <v>35</v>
-      </c>
-      <c r="B35" s="29" t="s">
+    <row r="37" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A37" s="28">
+        <v>37</v>
+      </c>
+      <c r="B37" s="28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="29">
-        <v>36</v>
-      </c>
-      <c r="B36" s="29" t="s">
+    <row r="38" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A38" s="28">
+        <v>38</v>
+      </c>
+      <c r="B38" s="28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A37" s="29">
-        <v>37</v>
-      </c>
-      <c r="B37" s="29" t="s">
+    <row r="39" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A39" s="28">
+        <v>39</v>
+      </c>
+      <c r="B39" s="28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="29">
-        <v>38</v>
-      </c>
-      <c r="B38" s="29" t="s">
+    <row r="40" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A40" s="28">
+        <v>40</v>
+      </c>
+      <c r="B40" s="28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="29">
-        <v>39</v>
-      </c>
-      <c r="B39" s="29" t="s">
+    <row r="41" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A41" s="28">
+        <v>41</v>
+      </c>
+      <c r="B41" s="28" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="29">
-        <v>40</v>
-      </c>
-      <c r="B40" s="29" t="s">
+    <row r="42" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A42" s="28">
+        <v>42</v>
+      </c>
+      <c r="B42" s="28" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A41" s="29">
-        <v>41</v>
-      </c>
-      <c r="B41" s="29" t="s">
+    <row r="43" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A43" s="28">
+        <v>43</v>
+      </c>
+      <c r="B43" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="29">
-        <v>42</v>
-      </c>
-      <c r="B42" s="29" t="s">
+    <row r="44" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A44" s="28">
+        <v>44</v>
+      </c>
+      <c r="B44" s="28" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="29">
-        <v>43</v>
-      </c>
-      <c r="B43" s="29" t="s">
+    <row r="45" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A45" s="28">
+        <v>45</v>
+      </c>
+      <c r="B45" s="28" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="29">
-        <v>44</v>
-      </c>
-      <c r="B44" s="29" t="s">
+    <row r="46" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A46" s="28">
+        <v>46</v>
+      </c>
+      <c r="B46" s="28" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A45" s="29">
-        <v>45</v>
-      </c>
-      <c r="B45" s="29" t="s">
+    <row r="47" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A47" s="28">
+        <v>47</v>
+      </c>
+      <c r="B47" s="28" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="29">
-        <v>46</v>
-      </c>
-      <c r="B46" s="29" t="s">
+    <row r="48" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A48" s="28">
+        <v>48</v>
+      </c>
+      <c r="B48" s="28" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="29">
-        <v>47</v>
-      </c>
-      <c r="B47" s="29" t="s">
+    <row r="49" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A49" s="28">
+        <v>49</v>
+      </c>
+      <c r="B49" s="28" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="29">
-        <v>48</v>
-      </c>
-      <c r="B48" s="29" t="s">
+    <row r="50" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A50" s="28">
+        <v>50</v>
+      </c>
+      <c r="B50" s="28" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="29">
-        <v>49</v>
-      </c>
-      <c r="B49" s="29" t="s">
+    <row r="51" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A51" s="28">
+        <v>51</v>
+      </c>
+      <c r="B51" s="28" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A50" s="29">
-        <v>50</v>
-      </c>
-      <c r="B50" s="29" t="s">
+    <row r="52" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A52" s="28">
+        <v>52</v>
+      </c>
+      <c r="B52" s="28" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A51" s="29">
-        <v>51</v>
-      </c>
-      <c r="B51" s="29" t="s">
+    <row r="53" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A53" s="28">
+        <v>53</v>
+      </c>
+      <c r="B53" s="28" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A52" s="29">
-        <v>52</v>
-      </c>
-      <c r="B52" s="29" t="s">
+    <row r="54" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A54" s="28">
+        <v>54</v>
+      </c>
+      <c r="B54" s="28" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A53" s="29">
-        <v>53</v>
-      </c>
-      <c r="B53" s="29" t="s">
+    <row r="55" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A55" s="28">
+        <v>55</v>
+      </c>
+      <c r="B55" s="28" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A54" s="29">
-        <v>54</v>
-      </c>
-      <c r="B54" s="29" t="s">
+    <row r="56" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A56" s="28">
+        <v>56</v>
+      </c>
+      <c r="B56" s="28" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A55" s="29">
-        <v>55</v>
-      </c>
-      <c r="B55" s="29" t="s">
+    <row r="57" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A57" s="28">
+        <v>57</v>
+      </c>
+      <c r="B57" s="28" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A56" s="29">
-        <v>56</v>
-      </c>
-      <c r="B56" s="29" t="s">
+    <row r="58" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A58" s="28">
+        <v>58</v>
+      </c>
+      <c r="B58" s="28" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A57" s="29">
-        <v>57</v>
-      </c>
-      <c r="B57" s="29" t="s">
+    <row r="59" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A59" s="28">
+        <v>59</v>
+      </c>
+      <c r="B59" s="28" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A58" s="29">
-        <v>58</v>
-      </c>
-      <c r="B58" s="29" t="s">
+    <row r="60" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A60" s="28">
+        <v>60</v>
+      </c>
+      <c r="B60" s="28" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A59" s="29">
-        <v>59</v>
-      </c>
-      <c r="B59" s="29" t="s">
+    <row r="61" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A61" s="28">
+        <v>61</v>
+      </c>
+      <c r="B61" s="28" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="29">
-        <v>60</v>
-      </c>
-      <c r="B60" s="29" t="s">
+    <row r="62" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A62" s="28">
+        <v>62</v>
+      </c>
+      <c r="B62" s="28" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="29">
-        <v>61</v>
-      </c>
-      <c r="B61" s="29" t="s">
+    <row r="63" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A63" s="28">
+        <v>63</v>
+      </c>
+      <c r="B63" s="28" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A62" s="29">
-        <v>62</v>
-      </c>
-      <c r="B62" s="29" t="s">
+    <row r="64" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A64" s="28">
+        <v>64</v>
+      </c>
+      <c r="B64" s="28" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="29">
-        <v>63</v>
-      </c>
-      <c r="B63" s="29" t="s">
+    <row r="65" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A65" s="28">
+        <v>65</v>
+      </c>
+      <c r="B65" s="28" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A64" s="29">
-        <v>64</v>
-      </c>
-      <c r="B64" s="29" t="s">
+    <row r="66" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A66" s="28">
+        <v>66</v>
+      </c>
+      <c r="B66" s="28" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A65" s="29">
-        <v>65</v>
-      </c>
-      <c r="B65" s="29" t="s">
+    <row r="67" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A67" s="28">
+        <v>67</v>
+      </c>
+      <c r="B67" s="28" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A66" s="29">
-        <v>66</v>
-      </c>
-      <c r="B66" s="29" t="s">
+    <row r="68" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A68" s="28">
+        <v>68</v>
+      </c>
+      <c r="B68" s="28" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A67" s="29">
-        <v>67</v>
-      </c>
-      <c r="B67" s="29" t="s">
+    <row r="69" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A69" s="28">
+        <v>69</v>
+      </c>
+      <c r="B69" s="28" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A68" s="29">
-        <v>68</v>
-      </c>
-      <c r="B68" s="29" t="s">
+    <row r="70" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A70" s="28">
+        <v>70</v>
+      </c>
+      <c r="B70" s="28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A69" s="29">
-        <v>69</v>
-      </c>
-      <c r="B69" s="29" t="s">
+    <row r="71" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A71" s="28">
+        <v>71</v>
+      </c>
+      <c r="B71" s="28" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A70" s="29">
-        <v>70</v>
-      </c>
-      <c r="B70" s="29" t="s">
+    <row r="72" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A72" s="28">
+        <v>72</v>
+      </c>
+      <c r="B72" s="28" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A71" s="29">
-        <v>71</v>
-      </c>
-      <c r="B71" s="29" t="s">
+    <row r="73" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A73" s="28">
+        <v>73</v>
+      </c>
+      <c r="B73" s="28" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A72" s="29">
-        <v>72</v>
-      </c>
-      <c r="B72" s="29" t="s">
+    <row r="74" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A74" s="28">
+        <v>74</v>
+      </c>
+      <c r="B74" s="28" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A73" s="29">
-        <v>73</v>
-      </c>
-      <c r="B73" s="29" t="s">
+    <row r="75" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A75" s="28">
+        <v>75</v>
+      </c>
+      <c r="B75" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="29">
-        <v>74</v>
-      </c>
-      <c r="B74" s="29" t="s">
+    <row r="76" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A76" s="28">
+        <v>76</v>
+      </c>
+      <c r="B76" s="28" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="29">
-        <v>75</v>
-      </c>
-      <c r="B75" s="29" t="s">
+    <row r="77" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A77" s="28">
+        <v>77</v>
+      </c>
+      <c r="B77" s="28" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A76" s="29">
-        <v>76</v>
-      </c>
-      <c r="B76" s="29" t="s">
+    <row r="78" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A78" s="28">
+        <v>78</v>
+      </c>
+      <c r="B78" s="28" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="29">
-        <v>77</v>
-      </c>
-      <c r="B77" s="29" t="s">
+    <row r="79" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A79" s="28">
+        <v>79</v>
+      </c>
+      <c r="B79" s="28" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A78" s="29">
-        <v>78</v>
-      </c>
-      <c r="B78" s="29" t="s">
+    <row r="80" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A80" s="28">
+        <v>80</v>
+      </c>
+      <c r="B80" s="28" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A79" s="29">
-        <v>79</v>
-      </c>
-      <c r="B79" s="29" t="s">
+    <row r="81" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A81" s="28">
+        <v>81</v>
+      </c>
+      <c r="B81" s="28" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A80" s="29">
-        <v>80</v>
-      </c>
-      <c r="B80" s="29" t="s">
+    <row r="82" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A82" s="28">
+        <v>82</v>
+      </c>
+      <c r="B82" s="28" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A81" s="29">
-        <v>81</v>
-      </c>
-      <c r="B81" s="29" t="s">
+    <row r="83" spans="1:2" ht="20" x14ac:dyDescent="0.2">
+      <c r="A83" s="28">
+        <v>83</v>
+      </c>
+      <c r="B83" s="28" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A82" s="29">
-        <v>82</v>
-      </c>
-      <c r="B82" s="29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="20" x14ac:dyDescent="0.2">
-      <c r="A83" s="29">
-        <v>83</v>
-      </c>
-      <c r="B83" s="29" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
